--- a/Results/LotScreening.xlsx
+++ b/Results/LotScreening.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,31 +513,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1040</v>
+        <v>1300</v>
       </c>
       <c r="D2" t="n">
-        <v>1040</v>
+        <v>1290</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>70.04653117279139</v>
+        <v>69.78074780276015</v>
       </c>
       <c r="G2" t="n">
-        <v>71.0496438272086</v>
+        <v>70.26459665877832</v>
       </c>
       <c r="H2" t="n">
-        <v>70.54808749999999</v>
+        <v>70.02232317829457</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1671854424028669</v>
+        <v>0.06919983239757115</v>
       </c>
       <c r="J2" t="n">
-        <v>1.003112654417201</v>
+        <v>0.4151989943854268</v>
       </c>
       <c r="K2" t="n">
-        <v>1.421884972313674</v>
+        <v>0.5929523265433868</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -547,7 +547,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0088, 0452, 0637, 0714, 1178, 1188, 1204, 1267, 1277, 1297</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -561,31 +565,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1040</v>
+        <v>1300</v>
       </c>
       <c r="D3" t="n">
-        <v>1037</v>
+        <v>1286</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>70.2311408635473</v>
+        <v>70.30126009125962</v>
       </c>
       <c r="G3" t="n">
-        <v>70.59030529029886</v>
+        <v>70.44289375489421</v>
       </c>
       <c r="H3" t="n">
-        <v>70.40962584378013</v>
+        <v>70.37279937791602</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04999748139641888</v>
+        <v>0.02180291759804766</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2999848883785133</v>
+        <v>0.1308175055882859</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4260566432267349</v>
+        <v>0.185892144045272</v>
       </c>
       <c r="L3" t="n">
         <v>2</v>
@@ -597,7 +601,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0139, 0212, 0314</t>
+          <t>0023, 0032, 0035, 0073, 0090, 0091, 0134, 0175, 0368, 0377, 0451, 0794, 0999, 1078</t>
         </is>
       </c>
     </row>
@@ -613,31 +617,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1032</v>
+        <v>1300</v>
       </c>
       <c r="D4" t="n">
-        <v>1014</v>
+        <v>1256</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>21.14316281178377</v>
+        <v>20.97537224315294</v>
       </c>
       <c r="G4" t="n">
-        <v>21.28280618046428</v>
+        <v>21.33388929530861</v>
       </c>
       <c r="H4" t="n">
-        <v>21.21183431952663</v>
+        <v>21.16242834394905</v>
       </c>
       <c r="I4" t="n">
-        <v>0.020132406037541</v>
+        <v>0.04314371583126378</v>
       </c>
       <c r="J4" t="n">
-        <v>0.120794436225246</v>
+        <v>0.2588622949875827</v>
       </c>
       <c r="K4" t="n">
-        <v>0.569467187069476</v>
+        <v>1.223216403998358</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -649,109 +653,9 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0003, 0010, 0116, 0136, 0139, 0148, 0216, 0246, 0278, 0295, 0441, 0458, 0554, 0557, 0597, 0630, 0798, 0834</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Initial ACIR</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Initial ACIR(mΩ)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>1040</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1039</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10.53384145344703</v>
-      </c>
-      <c r="G5" t="n">
-        <v>12.24196623886066</v>
-      </c>
-      <c r="H5" t="n">
-        <v>11.38707410972089</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.2835647298399308</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.701388379039585</v>
-      </c>
-      <c r="K5" t="n">
-        <v>14.94140077289168</v>
-      </c>
-      <c r="L5" t="n">
-        <v>15</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0330</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Voltage3.6</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Voltage3.6(V)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1040</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1040</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3.568194066720924</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.594682856356</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.581438461538462</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.004414798272512842</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.02648878963507705</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.7396131448171913</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>0005, 0007, 0008, 0010, 0011, 0012, 0013, 0014, 0015, 0016, 0018, 0019, 0020, 0021, 0022, 0023, 0024, 0025, 0026, 0027, 0028, 0029, 0030, 0033, 0035, 0036, 0037, 0038, 0044, 0052, 0053, 0054, 0058, 0062, 0063, 0068, 0069, 0070, 0077, 0134, 0135, 0140, 0141, 0142</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -764,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,7 +710,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.421884972313674</v>
+        <v>0.5929523265433868</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
@@ -829,7 +733,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4260566432267349</v>
+        <v>0.185892144045272</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -852,58 +756,12 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.569467187069476</v>
+        <v>1.223216403998358</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Initial ACIR</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Initial ACIR(mΩ)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>14.94140077289168</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Voltage3.6</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Voltage3.6(V)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.7396131448171913</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
